--- a/pdf2img/hasil_ekstraksi/table_6/tabel_1.xlsx
+++ b/pdf2img/hasil_ekstraksi/table_6/tabel_1.xlsx
@@ -1033,210 +1033,150 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="41" customWidth="1" min="1" max="1"/>
-    <col width="41" customWidth="1" min="2" max="2"/>
-    <col width="43" customWidth="1" min="3" max="3"/>
-    <col width="43" customWidth="1" min="4" max="4"/>
-    <col width="43" customWidth="1" min="5" max="5"/>
-    <col width="43" customWidth="1" min="6" max="6"/>
-    <col width="43" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
-    <col width="43" customWidth="1" min="9" max="9"/>
-    <col width="43" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="3" customWidth="1" min="4" max="4"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="5" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Unnamed: 1_level_0 | Unnamed: 1_level_1</t>
+          <t>column_2</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>Unnamed: 9_level_0 | Unnamed: 9_level_1</t>
+          <t>column_10</t>
         </is>
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
-          <t>Unnamed: 10_level_0 | Unnamed: 10_level_1</t>
+          <t>column_11</t>
         </is>
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t>Unnamed: 13_level_0 | Unnamed: 13_level_1</t>
+          <t>:</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
-          <t>Unnamed: 21_level_0 | Unnamed: 21_level_1</t>
+          <t>: M</t>
         </is>
       </c>
       <c r="F1" s="2" t="inlineStr">
         <is>
-          <t>Unnamed: 22_level_0 | Unnamed: 22_level_1</t>
+          <t>:_2</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
         <is>
-          <t>Unnamed: 23_level_0 | Unnamed: 23_level_1</t>
+          <t>1 E</t>
         </is>
       </c>
       <c r="H1" s="2" t="inlineStr">
         <is>
-          <t>Unnamed: 24_level_0 | 15</t>
+          <t>column_21</t>
         </is>
       </c>
       <c r="I1" s="2" t="inlineStr">
         <is>
-          <t>Unnamed: 28_level_0 | Unnamed: 28_level_1</t>
-        </is>
-      </c>
-      <c r="J1" s="2" t="inlineStr">
-        <is>
-          <t>Unnamed: 29_level_0 | Unnamed: 29_level_1</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr"/>
-      <c r="B2" s="3" t="inlineStr"/>
+      <c r="A2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
       <c r="C2" s="3" t="inlineStr"/>
-      <c r="D2" s="3" t="inlineStr"/>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>:</t>
-        </is>
-      </c>
+      <c r="D2" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="E2" s="3" t="inlineStr"/>
       <c r="F2" s="3" t="inlineStr"/>
       <c r="G2" s="3" t="inlineStr"/>
-      <c r="H2" s="3" t="inlineStr"/>
-      <c r="I2" s="3" t="inlineStr"/>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>:</t>
-        </is>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr"/>
       <c r="B3" s="3" t="inlineStr"/>
       <c r="C3" s="3" t="inlineStr"/>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr"/>
+      <c r="E3" s="3" t="inlineStr"/>
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>:</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr"/>
+      <c r="I3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr"/>
+      <c r="B4" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C4" s="3" t="inlineStr"/>
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>:</t>
         </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>1 E</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="J3" s="3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>:</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr"/>
-      <c r="D4" s="3" t="n">
-        <v>9</v>
       </c>
       <c r="E4" s="3" t="inlineStr"/>
       <c r="F4" s="3" t="inlineStr"/>
       <c r="G4" s="3" t="inlineStr"/>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr"/>
+      <c r="I4" s="3" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr"/>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>1 M</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>j</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr"/>
+      <c r="G5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="I4" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr"/>
-      <c r="B5" s="3" t="inlineStr"/>
-      <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="3" t="inlineStr"/>
-      <c r="E5" s="3" t="inlineStr"/>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>:</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr"/>
-      <c r="H5" s="3" t="inlineStr"/>
       <c r="I5" s="3" t="inlineStr"/>
-      <c r="J5" s="3" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr"/>
-      <c r="B6" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="C6" s="3" t="inlineStr"/>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>:</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr"/>
-      <c r="F6" s="3" t="inlineStr"/>
-      <c r="G6" s="3" t="inlineStr"/>
-      <c r="H6" s="3" t="inlineStr"/>
-      <c r="I6" s="3" t="inlineStr"/>
-      <c r="J6" s="3" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B7" s="3" t="inlineStr"/>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>1 M</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr"/>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>j</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr"/>
-      <c r="J7" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
